--- a/Material_Testing_Review.xlsx
+++ b/Material_Testing_Review.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Empty" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Shoulder HSV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Shoulder NDG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Shoulder SRT" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -26,12 +31,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+        <bgColor rgb="00FFCCCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +427,2628 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Tested</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Hand Vane Shear Strength</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream  Shoulder Upstream , L003-HL-010-HSV, SU7234 0976, 32.254mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream  Shoulder Upstream , L003-HL-011-HSV, SU7234 0978, 32.545mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream  Shoulder Upstream , L003-HL-012-HSV, SU7238 0978, 32.572mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream  Shoulder Upstream , L003-HL-013-HSV, SU7233 0978, 32.378mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream  Shoulder Upstream , L003-HL-014-HSV, SU7231 0977, 32.043mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-HL-015-HSV, SU7232 0975, 31.855mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream, L009-CE-006-HSV, SU7089 0981, 33.193mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-007-HSV, SU7089 0983, 33.729mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-008-HSV, SU7089 0984, 34.096mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-009-HSV, SU7087 0982, 34.349mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-010-HSV, SU7087 0982, 33.855mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-011-HSV, SU7087 0980, 33.471mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-012-HSV, SU7084 0978, 33.275mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-013-HSV, SU7085 0979, 33.587mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-014-HSV, SU7085 0982, 34.051mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-015-HSV, SU7085 0985, 34.405mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L003-CE-001-HSV, SU7085 0987, 33.842mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L003-CE-002-HSV, SU7086 0990, 34.380mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L003-CE-003-HSV, SU7086 0993, 35.078mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L003-CE-004-HSV, SU7085 0995, 35.625mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L003-CE-005-HSV, SU7086 0997, 36.110mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L005-TW-001-HSV, SU7128 0943, 20.580mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L005-TW-003-HSV, SU7126 0944, 20.980mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L005-TW-004-HSV, SU7127 0947, 21.429mA0D, L5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L005-TW-002 HSV, SU 7129 0943, 20.683mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Downstream  Shoulder Downstream , Chamber 6A (3D), 3D L003-CE-001, SU 7077 0970, 33.749mAOD</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L010-CE-004-HSV, SU7082 0964, 32.954mA0D, L10</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L010--CE-005-HSV, SU7083 0961, 34.736mAOD, L10</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L010-CE-006-HSV, SU7085 0961, 34.552mAOD, L10</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L006-TW-003-HSV, SU7125 0946, 22.248mAOD, L6</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 140</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L006-CE-004-HSV, SU7126 0947, 21.856mAOD, L6</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 140</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L006-TW-005-HSV, SU7126 0946, 21.716mA0D, L6</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 140</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream , L005-CE-001-HSV, SU 7087 0988, 34.283mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream , L005-CE-002-HSV, SU 7087 0991, 34.796mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream , L005-CE-003-HSV, SU 7087 0993, 35.460mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream , L005-CE-004-HSV, SU 7087 0995, 35.792mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Tested</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Dry Density</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Degree of Compaction</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Air Voids</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream Shoulder Upstream, L003-HL-010-NFD, SU 7234 0976, 32.254mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="F2" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream Shoulder Upstream, L003-HL-011-NFD, SU 7234 0978, 32.545mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="F3" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream Shoulder Upstream, L003-HL-012-NFD, SU 7233 0978, 32.572mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="F4" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream Shoulder Upstream, L003-HL-013-NFD, SU 7233 0978, 32.378mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="F5" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream Shoulder Upstream, L003-HL-014-NFD, SU 7231 0977, 32.043mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1.471</v>
+      </c>
+      <c r="F6" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ME-GIZ East Shoulder Upstream Shoulder Upstream, L003-HL-015-NFD, SU 7232 0975, 31.855mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1.451</v>
+      </c>
+      <c r="F7" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009-CE-006-NFD, SU 7089 0981, 33.193mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="F8" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009-CE-007-NFD, SU 7089 0983, 33.729mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009-CE-008-NFD, SU 7089 0984, 34.096mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1.471</v>
+      </c>
+      <c r="F10" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009-CE-009-NFD, SU 7087 0985, 34.349mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="F11" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009-CE-010-NFD, SU 7087 0982, 33.855mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="F12" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009-CE-011-NFD, SU 7087 0980, 33.471mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1.468</v>
+      </c>
+      <c r="F13" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009- CE-012-NFD, SU 7084 0978, 33.275mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1.534</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009- CE-013-NFD, SU 7085 0979, 33.587mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1.446</v>
+      </c>
+      <c r="F15" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009-CE-014-NFD, SU 7085 0982, 34.051mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="F16" t="n">
+        <v>96</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L009-CE-015-NFD, SU 7085 0985, 34.405mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="F17" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L003-CE-001-NFD, SU 7085 0987, 33.842mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="F18" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L003-CE-002-NFD, SU 7086 0990, 34.380mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F19" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L003-CE-003-NFD, SU 7086 0993, 35.078mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="F20" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L003-CE-004-NFD, SU 7085 0995, 35.625mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="F21" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L003-CE-005-NFD, SU 7085 0997, 36.110mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="F22" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L005-TW-001-NFD, SU 7128 0943, 20.580mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="F23" t="n">
+        <v>97</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L005-TW-003-NFD, SU 7126 0944, 20.980mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="F24" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L005-TW-004-NFD, SU 7127 0947, 21.429mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="F25" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L005-TW-002-NFD, SU 7129 0943, 20.683mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="F26" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Head Clay</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Downstream Shoulder Downstream Chamber 6A (3D), 3D L003-CE-001-NFD, SU 7077 0970, 33.749mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="F27" t="n">
+        <v>97</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Head Clay</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L010-CE-004-NFD, SU 7082 0964, 32.954mAOD, L10</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="F28" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Head Clay</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L010-CE-005-NFD, SU 7083 0961, 34.746mAOD, L10</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="F29" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Head Clay</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream, L010-CE-006-NFD, SU 7085 0961, 34.552mAOD, L10</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="F30" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reading Clay </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Downstream Shoulder Downstream , L006-TW-001-NFD, SU 7128 0949, 19.191mAOD, L6</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="F31" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reading Clay </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Downstream Shoulder Downstream , L006-TW-002-NFD, SU 7130 0941, 19.258mAOD, L6</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F32" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reading Clay </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Downstream Shoulder Downstream , L006-TW-004-NFD, SU 7126 0947, 21.856mAOD, L6</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F33" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream , L005-CE-001-NFD, SU 7087 0988, 34.283mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="F34" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream , L005-CE-002-NFD, SU 7087 0991, 34.796mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream , L005-CE-003-NFD, SU 7087 0993, 35.460mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F36" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream Shoulder Upstream , L005-CE-004-NFD, SU 7087 0995, 35.792mAOD, L5</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="F37" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Tested</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SRD Dry Density</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Degree of Compaction</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SRD Air Voids</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L003-AJ-012 SRT , SU 7233 0978, 32.572mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L003-AT-CE-001 SRT, SU 7085 0987, 33.842mAOD, L3</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="F3" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-007 SRT, SU 7089 0983, 33.729mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="F4" t="n">
+        <v>99</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WLC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Upstream  Shoulder Upstream , L009-CE-009 SRT, SU 7087 0985, 34.349mAOD, L9</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.503</v>
+      </c>
+      <c r="F5" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reading Clay </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ME-GIZ West Shoulder Downstream  Shoulder Downstream , L006-TW-003 SRT, SU 7125 0946, 22.248mAOD, L6</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1.631</v>
+      </c>
+      <c r="F6" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>